--- a/produits/preuves/sortie/recherchev-sierreur/recherchev-sierreur.xlsx
+++ b/produits/preuves/sortie/recherchev-sierreur/recherchev-sierreur.xlsx
@@ -248,6 +248,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="4.9"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -309,8 +310,9 @@
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="4.9"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
